--- a/outputs/counterparty_risk_calculations.xlsx
+++ b/outputs/counterparty_risk_calculations.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Raw_Exposures" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Aggregated_Exposures" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="V_Inter_Calculations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Aggregation_Tree" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,145 +445,188 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>LEI Code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SCR Ratio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>MCR Ratio</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Market Value</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RI Deposits</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>RI &gt; 60% tied up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Risk Mitigating Effect</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Risk adjustet Mortgage</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Morgage Guarantee</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Market Value Collateral</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Collateral Adjustment</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>3rd Party Requirement</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Collataral Insolvency</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Simplified Collateral</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pool Name</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Pool Type</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Pool SII Scope</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Pool EOF</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Pool SoR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Pool USoR</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Pool &gt;= 60% Collateral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Pool RM Contribution</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Pool SII Ratio</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RACollateral</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>LGD</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>LGD_Base</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>eof_pool_ratio</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>sor_pool_ratio</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>aggregated_Pool EOF</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>aggregated_Pool SoR</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>aggregated_Pool SII Ratio</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>aggregated_EOF/Pool SII Ratio</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>aggregated_SoR * Pool SII Ratio</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
@@ -599,85 +643,100 @@
           <t>Counterparty A1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>2000</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Pooling arrangements A</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>55000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U2" t="n">
-        <v>870.0216165416232</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2e-05</v>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Pooling arrangements A</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="W2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>28061.22448979592</v>
-      </c>
+        <v>55000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>58600</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
         <v>1.96</v>
       </c>
       <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1566.038909774922</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>28061.22448979592</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>58600</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL2" t="n">
         <v>30297.24933451641</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AM2" t="n">
         <v>0.00375</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AN2" t="n">
         <v>0.8700216165416232</v>
       </c>
     </row>
@@ -692,85 +751,100 @@
           <t>Counterparty A2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>500</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Pooling arrangements A</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0.005</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Pooling arrangements A</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
         <v>0.75</v>
       </c>
-      <c r="U3" t="n">
-        <v>217.5054041354058</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>391.5097274437305</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0.042</v>
       </c>
-      <c r="W3" t="n">
-        <v>250</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
+      <c r="AF3" t="n">
+        <v>450</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
         <v>0.00375</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AI3" t="n">
         <v>58600</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AJ3" t="n">
         <v>0.005</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AK3" t="n">
         <v>1.96</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AL3" t="n">
         <v>30297.24933451641</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AM3" t="n">
         <v>0.00375</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AN3" t="n">
         <v>0.8700216165416232</v>
       </c>
     </row>
@@ -785,85 +859,100 @@
           <t>Counterparty A3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
         <v>1.61</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1.5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>15000</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Pooling arrangements A</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3600</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Pooling arrangements A</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>3600</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
         <v>1.61</v>
       </c>
-      <c r="U4" t="n">
-        <v>6525.162124062174</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11745.29182331191</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0.0007799999999999999</v>
       </c>
-      <c r="W4" t="n">
-        <v>7500</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AF4" t="n">
+        <v>13500</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2236.024844720497</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
         <v>58600</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AJ4" t="n">
         <v>0.005</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AK4" t="n">
         <v>1.96</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AL4" t="n">
         <v>30297.24933451641</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AM4" t="n">
         <v>0.00375</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AN4" t="n">
         <v>0.8700216165416232</v>
       </c>
     </row>
@@ -878,71 +967,98 @@
           <t>Counterparty B1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>BBB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>100000</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>100</v>
       </c>
-      <c r="K5" t="n">
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>Pooling arrangements B</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U5" t="n">
-        <v>12450</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="W5" t="n">
-        <v>49950</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
-        <v>0.305</v>
-      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12482</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>89984.7</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -955,71 +1071,98 @@
           <t>Counterparty B2</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>5500</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>50</v>
       </c>
-      <c r="K6" t="n">
+      <c r="P6" t="n">
         <v>10</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Pooling arrangements B</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U6" t="n">
-        <v>662.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2725</v>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>0.2375</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>678.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4943.52</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1032,71 +1175,98 @@
           <t>Counterparty B3</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>7032</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>2000</v>
       </c>
-      <c r="K7" t="n">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>Pooling arrangements B</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2516</v>
-      </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="n">
-        <v>0.1875</v>
-      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>519</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>6058.8</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1109,71 +1279,98 @@
           <t>Counterparty BB1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>CCC or lower</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>100000</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>100</v>
       </c>
-      <c r="K8" t="n">
+      <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>Pooling arrangements BB</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
         <v>0.3333</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>16615</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="W8" t="n">
-        <v>49950</v>
-      </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="n">
-        <v>0.249975</v>
-      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>16647</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>89984.7</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>0.249975</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1186,71 +1383,98 @@
           <t>Counterparty BB2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>CCC or lower</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>5500</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>50</v>
       </c>
-      <c r="K9" t="n">
+      <c r="P9" t="n">
         <v>10</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>Pooling arrangements BB</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
         <v>0.3333</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>891.5749999999999</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2725</v>
-      </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="n">
-        <v>0.249975</v>
-      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>907.5749999999999</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4943.52</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>0.249975</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1263,69 +1487,96 @@
           <t>Counterparty C1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>CCC or lower</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>100</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>50</v>
       </c>
-      <c r="K10" t="n">
+      <c r="P10" t="n">
         <v>5</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>Pooling arrangements C1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
         <v>0.3333</v>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="W10" t="n">
-        <v>25</v>
-      </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>7.664999999999999</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1338,69 +1589,96 @@
           <t>Counterparty C2</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Ceding reinsurance</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>CCC or lower</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>222221</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>300</v>
       </c>
-      <c r="K11" t="n">
+      <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>Pooling arrangements C2</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
         <v>0.3333</v>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>36883.12965</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="W11" t="n">
-        <v>110960.5</v>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>255</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>36979.12965</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>199953</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1440,7 +1718,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>870.0216165416232</v>
+        <v>1566.038909774922</v>
       </c>
       <c r="C2" t="n">
         <v>2e-05</v>
@@ -1453,7 +1731,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>217.5054041354058</v>
+        <v>391.5097274437305</v>
       </c>
       <c r="C3" t="n">
         <v>0.042</v>
@@ -1466,7 +1744,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6525.162124062174</v>
+        <v>11745.29182331191</v>
       </c>
       <c r="C4" t="n">
         <v>0.0007799999999999999</v>
@@ -1479,7 +1757,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12450</v>
+        <v>12482</v>
       </c>
       <c r="C5" t="n">
         <v>0.0024</v>
@@ -1492,7 +1770,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>662.5</v>
+        <v>678.5</v>
       </c>
       <c r="C6" t="n">
         <v>0.012</v>
@@ -1505,9 +1783,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>519</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.042</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1516,7 +1796,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16615</v>
+        <v>16647</v>
       </c>
       <c r="C8" t="n">
         <v>0.042</v>
@@ -1529,10 +1809,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>891.5749999999999</v>
+        <v>907.5749999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04200000000000001</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="10">
@@ -1542,9 +1822,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>7.664999999999999</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.042</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1553,7 +1835,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36883.12965</v>
+        <v>36979.12965</v>
       </c>
       <c r="C11" t="n">
         <v>0.042</v>
@@ -1570,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,10 +1877,10 @@
         <v>2e-05</v>
       </c>
       <c r="B2" t="n">
-        <v>870.0216165416232</v>
+        <v>1566.038909774922</v>
       </c>
       <c r="C2" t="n">
-        <v>9.083142359108086</v>
+        <v>29.42938124351019</v>
       </c>
     </row>
     <row r="3">
@@ -1606,10 +1888,10 @@
         <v>0.0007799999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>6525.162124062174</v>
+        <v>11745.29182331191</v>
       </c>
       <c r="C3" t="n">
-        <v>19917.05421123057</v>
+        <v>64531.25564438706</v>
       </c>
     </row>
     <row r="4">
@@ -1617,10 +1899,10 @@
         <v>0.0024</v>
       </c>
       <c r="B4" t="n">
-        <v>12450</v>
+        <v>12482</v>
       </c>
       <c r="C4" t="n">
-        <v>222881.8779628443</v>
+        <v>224029.0885652787</v>
       </c>
     </row>
     <row r="5">
@@ -1628,10 +1910,10 @@
         <v>0.012</v>
       </c>
       <c r="B5" t="n">
-        <v>662.5</v>
+        <v>678.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3137.262359324759</v>
+        <v>3290.627915594855</v>
       </c>
     </row>
     <row r="6">
@@ -1639,10 +1921,10 @@
         <v>0.042</v>
       </c>
       <c r="B6" t="n">
-        <v>217.5054041354058</v>
+        <v>391.5097274437305</v>
       </c>
       <c r="C6" t="n">
-        <v>1161.620542872059</v>
+        <v>3763.650558905472</v>
       </c>
     </row>
     <row r="7">
@@ -1650,21 +1932,10 @@
         <v>0.042</v>
       </c>
       <c r="B7" t="n">
-        <v>53498.12965</v>
+        <v>55060.36964999999</v>
       </c>
       <c r="C7" t="n">
-        <v>70275084.71074596</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.04200000000000001</v>
-      </c>
-      <c r="B8" t="n">
-        <v>891.5749999999999</v>
-      </c>
-      <c r="C8" t="n">
-        <v>19518.20811824298</v>
+        <v>74439324.83482526</v>
       </c>
     </row>
   </sheetData>
@@ -1678,6 +1949,872 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AGGREGATION_TREE_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>NODE_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PARENT_NODE_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>NODE_DESC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AGGREGATION_METHOD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MATRIX_ID</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MAX_SCENARIO_BASE</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>BS_TYPE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SCENARIO</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Counterparty C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Counterparty BB1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Counterparty B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_04</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Counterparty A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Counterparty A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Counterparty BB2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Counterparty B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Counterparty B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Counterparty A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PARENT_GROUP_10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Counterparty C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LGD_01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>36979.12965</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LGD_02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>16647</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LGD_03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>12482</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LGD_04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>11745.29182331191</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LGD_05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>1566.038909774922</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LGD_06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>907.5749999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LGD_07</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>678.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LGD_08</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LGD_09</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>391.5097274437305</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LGD_10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>7.664999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PD_01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PD_02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PD_03</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>0.0024</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PD_04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>0.0007799999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PD_05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>2e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PD_06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PD_07</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PD_08</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PD_09</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CPD_TYPE1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PD_10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>calculate_cpty_type1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1700,7 +2837,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70541709.81708284</v>
+        <v>74734968.88689066</v>
       </c>
     </row>
     <row r="3">
@@ -1710,7 +2847,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50333316.80627199</v>
+        <v>52299501.40168203</v>
       </c>
     </row>
     <row r="4">
@@ -1720,7 +2857,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10994.317924426</v>
+        <v>11270.95693757068</v>
       </c>
     </row>
   </sheetData>
